--- a/important_mails_2026-06-01.xlsx
+++ b/important_mails_2026-06-01.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,215 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Mon, 1 Jun 2026 02:40:59 +0000</t>
+          <t>Mon, 1 Jun 2026 14:58:44 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Transparency Invoice/Credit note for 05/2026</t>
+          <t>Your payment is on the way</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement attempted
+Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
+On 06/01/26 14:57 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
+ 287.55.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon Store,
+Amazon Services
+Help us improve your payment experience on Amaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 1 Jun 2026 10:39:43 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"cscompliance-docreview-seller@amazon.se" &lt;cscompliance-docreview-seller@amazon.se&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
+ A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review
+ Do not reply back to this e-mail!
+Hello,
+Thank you for submitting a document to the Chemical Safety Compliance Team.
+● The document uploaded for "B0DD7R3PPG" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
+→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
+The SDS does not include the legislation/regulation in accordance with the document was created
+Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
+For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
+Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these product/other products, please submit them ( for each ASIN separately ) in "Account Health Dashboard" under the relevant Appeal reason:
+1. Go to the</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 1 Jun 2026 16:55:18 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Logística Multicanal de Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Ahorra un 20 % en las tarifas de Logística Multicanal a partir del 25 de junio</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Ya están disponibles dos nuevos programas de descuentos para los vendedores aptos
+ Hola:
+ Vamos a lanzar dos nuevos programas para ayudarte a ahorrar en las tarifas de Logística Multicanal.
+ A partir del 25 de junio de 2026, podrás ahorrar un 20 % al utilizar Logística Multicanal para entregar pedidos desde cualquier canal de venta externo a Amazon, como tu propio sitio web, tiendas de redes sociales como TikTok Shop, u otros sitios web como eBay.
+ Logística Multicanal puede ayudarte a hacer crecer tu negocio, ya que simplifica tus operaciones y proporciona a tus clientes un servicio de entrega rápido y fiable en paquetes sin marca, los siete días de la semana.
+ 1. Incentivos para vendedores nuevos:
+ si eres un vendedor nuevo de nuestro plan de ventas Profesional y publicas tu primer ASIN apto para la venta a partir del 25 de junio de 2026, puedes recibir un descuento del 20 % en las tarifas de gestión logística de Logística Multicanal para las 100 primeras unidades enviadas durante 12 meses. Para ello, tienes que enviar productos aptos de Logística de Amazon a nuestra red logística en un plazo de 90 días a partir de la publicación de tu primer ASIN apto para la venta.
+ A parti</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 1 Jun 2026 16:38:54 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Il team di Gestione multicanale di Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Tariffe di Gestione multicanale: sconto del 20% dal 25 giugno</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Due nuovi programmi di sconto sono ora disponibili per i venditori idonei
+ Buongiorno,
+ abbiamo deciso di lanciare due nuovi programmi per aiutare i venditori a risparmiare sulle tariffe di Gestione multicanale.
+ A partire dal 25 giugno 2026, potrai risparmiare il 20% quando utilizzi Gestione multicanale per consegnare ordini provenienti da qualsiasi canale di vendita diverso da Amazon, come il tuo sito web, i social media come TikTok Shop o altri siti come eBay.
+ Gestione multicanale può aiutarti a far crescere la tua attività semplificando le operazioni e offrendo ai clienti consegne rapide e affidabili in imballaggi privi di marchio, tutti i giorni della settimana.
+ 1. Incentivi per nuovi venditori:
+ Se sei un nuovo venditore con piano di vendita Professionale e pubblichi il tuo primo ASIN acquistabile a partire dal 25 giugno 2026, puoi ottenere uno sconto del 20% sulle tariffe di Gestione multicanale per le tue prime 100 unità di Gestione multicanale spedite nell'arco di 12 mesi. Per soddisfare i requisiti, devi inviare i prodotti Logistica di Amazon idonei alla nostra rete logistica entro 90 giorni dalla pubblicazione del tuo primo ASIN acquistabile.
+ A partire dal 25 giug</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 1 Jun 2026 02:40:59 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Transparency Invoice/Credit note for 05/2026</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -532,39 +726,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 00:17:48 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -594,39 +788,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:43:35 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $143.78 in an attempt to settle your Amazon seller account balance.
@@ -642,39 +836,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 01:13:32 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq5h330940)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -699,39 +893,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 06:55:02 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7kDrHSJf1h)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -751,39 +945,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 03:26:42 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -799,39 +993,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 13:57:34 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Iot4D83CtY)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -851,39 +1045,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:36 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -903,39 +1097,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -955,39 +1149,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 14:37:25 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1004,39 +1198,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1056,39 +1250,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:43:44 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1108,39 +1302,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:42:27 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1160,39 +1354,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 14:51:20 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -1208,39 +1402,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 13:35:40 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1257,92 +1451,40 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 25 May 2026 14:39:47 +0000</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement attempted
-Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
-On 05/25/26 14:39 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
- 350.61.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon Store,
-Amazon Services
-Help us improve your payment experience on Amaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:31:42 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS -
  APPEAL</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS - APPEAL
@@ -1363,39 +1505,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:48 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1413,39 +1555,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:09:04 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1463,39 +1605,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:43 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1513,39 +1655,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:07:21 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1563,39 +1705,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 06:06:12 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>帮您免费一站式搞定VAT、EPR等合规问题！亚马逊合规服务商城现已正式上线！</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>亚马逊合规服务商城正式上线，一站式帮助卖家高效搞定欧洲站点的VAT、EPR等合规问题。
 			尊敬的 深圳市微海众信科技有限公司,
@@ -1625,39 +1767,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 17:40:38 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1676,40 +1818,40 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 11:02:38 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -1722,39 +1864,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:40 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -1770,39 +1912,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:32 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -1816,40 +1958,40 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:31 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -1865,39 +2007,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:08:15 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -1913,40 +2055,40 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 15:14:09 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -1962,39 +2104,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 15:14:03 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -2010,39 +2152,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:04 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -2058,39 +2200,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:01 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -2104,40 +2246,40 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:00 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -2153,39 +2295,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:07:29 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -2201,39 +2343,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 15:12:02 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -2249,40 +2391,40 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2298,39 +2440,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 23:39:40 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para junio</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para junio
@@ -2359,39 +2501,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 17:10:26 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -2407,40 +2549,40 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 15:13:11 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Tu cuenta cumple ahora nuestros requisitos de registro a efectos
  fiscales en Europa</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -2465,39 +2607,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 15:09:37 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Twoje konto spełnia już europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -2522,39 +2664,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 10:15:12 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -2584,39 +2726,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Tue, 26 May 2026 12:22:30 +0000 (UTC)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>TikTok Shop &lt;tiktokshopseller@shop.tiktok.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>借助这些高潜力商品加速你的业务成长</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  借助这些高潜力商品加速你的业务成长
@@ -2709,89 +2851,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 25 May 2026 17:10:44 +0000</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Worten Marketplace - Portugal y España</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Hola Weihai EU,
-Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
-Nuestro equipo de análisis ha señalado que una asociación con usted sería una gran oportunidad para ambos.
-¿Estaría disponible para una reunión online esta semana?
-Acerca de Worten - Somos el líder del mercado portugués:
-- Nº 1 del comercio electrónico portugués
-- Sitio web con mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
-- Más de 200 tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
-- Plataforma de gestión: Mirakl (se puede integrar manualmente o vía API)
-- Sin costes iniciales - 6 meses
-Estaré encantado de ayudarle si tiene alguna pregunta.
-Muchas gracias,
-Saludos Cordiales</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 20:10:01 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
@@ -2807,39 +2899,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 04:57:03 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-11</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2862,39 +2954,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 03:41:21 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2918,39 +3010,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 03:00:56 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2973,39 +3065,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 02:44:04 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (y8kVKdPDvp)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3025,39 +3117,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:33:15 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $105.47 in an attempt to settle your Amazon seller account balance.
@@ -3073,39 +3165,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 02:39:33 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -3131,39 +3223,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3179,39 +3271,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3236,39 +3328,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3288,39 +3380,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3340,39 +3432,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3392,39 +3484,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3445,39 +3537,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3497,39 +3589,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3549,39 +3641,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -3597,39 +3689,91 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 25 May 2026 14:39:47 +0000</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement attempted
+Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
+On 05/25/26 14:39 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
+ 350.61.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon Store,
+Amazon Services
+Help us improve your payment experience on Amaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:30:35 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3649,39 +3793,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:29:45 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3698,39 +3842,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:22:00 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3750,39 +3894,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:11 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3802,39 +3946,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:21:19 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -3851,39 +3995,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:07:05 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January-March 2026</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -3900,39 +4044,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 14:48:57 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3952,39 +4096,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:42 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -4008,39 +4152,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:19 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -4064,39 +4208,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 13:46:45 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4116,39 +4260,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:49:45 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4168,39 +4312,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:47:51 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4220,39 +4364,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:36:52 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4272,39 +4416,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:51:22 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -4320,39 +4464,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:50:04 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4369,39 +4513,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:49:55 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4421,39 +4565,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -4470,39 +4614,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4519,39 +4663,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4571,39 +4715,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4623,39 +4767,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4672,39 +4816,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -4719,39 +4863,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -4767,144 +4911,40 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 2 May 2026 15:23:38 +0000</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>跨账户负余额调整</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- 我们已于 五月 2, 2026使用您的 Amazon.es 账户中的可用资金调整了您的 Amazon.de 卖家账户上应付的 €69.53 的负余额。通过登录您的账户并导航至 付款控制面板 ，您可以随时查看您的账户余额。
-有关更多信息，请访问 跨账户负余额调整 。
-诚挚的问候！
-欧洲亚马逊 Payments
- 报告此电子邮件的问题
- 如有任何疑问，请访问： 卖家平台
- 要更改您的电子邮件首选项，请访问： 通知首选项
- 2026 Amazon, Inc. 或其附属公司。保留所有权利。
- 欧洲亚马逊 Payments S.C.A.（société en Commandite par actions），是一家在卢森堡注册的股份有限公司，注册号（RCS Luxembourg）B 153 265，公司总部位于 38 avenue J.F.Kennedy, L-1855 Luxembourg。增值税编号为 LU 24448288。
- 欧洲亚马逊 Payments S.C.A. 由卢森堡金融行业监管委员会授权，并由爱尔兰中央银行对其业务行为规则的遵守情况进行监管。
- 亚马逊 Payments 是欧洲亚马逊 Payments S.C.A. 的商业名称。
- 此电子邮件发送自不受监控的电子邮件地址。
- SPC-EUAmazon-1724035883551525</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 1 May 2026 23:31:40 +0000</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 05/01/26 23:31 GST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of AED
- 136.70.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Am</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:58:41 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.ca" &lt;cscompliance-docreview-vendor@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC - DOC REVIEW
@@ -4921,40 +4961,40 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:53:39 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -4971,40 +5011,40 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:49:38 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC - DOC REVIEW
@@ -5021,39 +5061,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:02:52 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -5073,40 +5113,40 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:57:24 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -5122,40 +5162,40 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:55:04 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.fr" &lt;cscompliance-docreview-seller@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review
@@ -5171,39 +5211,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:11:27 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -5222,40 +5262,40 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5271,40 +5311,40 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5318,40 +5358,40 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5365,40 +5405,40 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -5411,39 +5451,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -5463,39 +5503,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -5520,39 +5560,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -5577,40 +5617,40 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5625,40 +5665,40 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5672,40 +5712,40 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5719,41 +5759,41 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -5764,39 +5804,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -5815,39 +5855,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5871,39 +5911,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5921,39 +5961,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5971,60 +6011,10 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 2 May 2026 13:15:01 +0000</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -6039,35 +6029,35 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Sat, 2 May 2026 02:13:49 +0000</t>
+          <t>Mon, 25 May 2026 17:10:44 +0000</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to reactivate listings</t>
+          <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listing?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
+          <t>Hola Weihai EU,
+Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
+Nuestro equipo de análisis ha señalado que una asociación con usted sería una gran oportunidad para ambos.
+¿Estaría disponible para una reunión online esta semana?
+Acerca de Worten - Somos el líder del mercado portugués:
+- Nº 1 del comercio electrónico portugués
+- Sitio web con mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
+- Más de 200 tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
+- Plataforma de gestión: Mirakl (se puede integrar manualmente o vía API)
+- Sin costes iniciales - 6 meses
+Estaré encantado de ayudarle si tiene alguna pregunta.
+Muchas gracias,
+Saludos Cordiales</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8685,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -8710,273 +8700,21 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Sat, 2 May 2026 15:27:47 +0600</t>
+          <t>Sat, 23 May 2026 04:06:08 +0000</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Amazon Review Rating Deals</t>
+          <t>Create FBA removal order by 2026-06-04</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>Not getting sales on Amazon? Even after doing everything right? Then this
-message is for you!
-Have you properly created your Amazon seller account, selected a good
-product, used strong keywords - yet still getting very low sales?
- The problem is simple — your product lacks trustworthy reviews and ratings!
-Today’s customers check reviews first, then decide to buy.without strong
-reviews—sales won’t come.
- That’s where we come in!
-We have Amazon Top Reviewers + Vine Buyers from Germany 🇩🇪, Spain 🇪🇸,
-Italy 🇮🇹, USA 🇺🇸, UK 🇬🇧, Canada 🇨🇦, and France 🇫🇷.
-✅ What we offer:
-⭐ 5-Star Text Reviews
-📸 5-Star Photo Reviews
-🎥 5-Star Video Reviews
-👉 All from real and authentic buyers!
-If you are satisfied with the review rating, you will provide a full refund
-to the buyer. For each review, you will also pay me a commission.
-✨ We manage your feedback, handle your reviews, and take your business to
-the next level!
-📩 Interested? Contact us now!
-👇 +1 (778) 721-5486</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 2 May 2026 03:15:52 +0000</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>Dien productveiligheidsdocumentatie in om productvermeldingen
- opnieuw te activeren</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
- Hallo Weihai EU,
- Sommige van je productvermeldingen zijn gedeactiveerd omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
- Waarom gebeurt dit?
- We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid. We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
- De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
- Hoe activeer ik mijn productvermeldingen opnieuw?
- Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
--
- Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen. We zullen alleen </t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 2 May 2026 02:15:51 +0000</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
- le offerte</t>
-        </is>
-      </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>96
- Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
- Gentile Weihai EU,
- Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
- Ciò a cosa è dovuto?
- Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
- La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
- Come faccio a riattivare le mie offerte?
- Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
--
- Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 2 May 2026 02:15:45 +0000</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>96
- Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
- Hej Weihai EU!
- Vissa av dina produktposter har inaktiverats på grund av att det saknas obligatorisk överensstämmelse för dina produkter. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
- Varför händer det här?
- Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer. Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
- Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
- Hur återaktiverar jag mina produktposter?
- Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
--
- Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna. Vi återaktiverar endast produkter som u</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 2 May 2026 01:23:15 +0000</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>96
- Presenta la documentación sobre seguridad del producto para reactivar los listings
- Hola, Weihai EU:
- Algunos de tus listings se han desactivado debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
- ¿A qué se debe esto?
- Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos . Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar una decisión.
- En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
- ¿Cómo puedo reactivar mis listings?
- Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
--
- Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cum</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 23 May 2026 04:06:08 +0000</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-06-04</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8999,39 +8737,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 03:17:21 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9055,39 +8793,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 04:51:55 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9111,39 +8849,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:58:34 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9164,39 +8902,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:50:26 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9219,39 +8957,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9275,39 +9013,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9330,96 +9068,40 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 2 May 2026 04:46:00 +0000</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- toabAY9R4I
- Unsellable Products:
-- FNSKU: X0025OEJ4F Quantity: 1
-- FNSKU: X002A05YW5 Quantity: 2
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 07:25:40 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Update VAT registration information to reinstate Inventory and FBA
  functionality of your Amazon.it store</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -9435,39 +9117,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96

--- a/important_mails_2026-06-01.xlsx
+++ b/important_mails_2026-06-01.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H173"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>店铺绩效类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,78 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Mon, 1 Jun 2026 14:58:44 +0000</t>
+          <t>Mon, 1 Jun 2026 19:29:32 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your payment is on the way</t>
+          <t>Your FBA request is complete (260520getf)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+Disposal Summary:
+Quantity Requested: 3
+Quantity Successfully Destroyed: 3
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-3657435-8840459
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-334253755000365</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 1 Jun 2026 14:58:44 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -534,40 +591,40 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 10:39:43 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.se" &lt;cscompliance-docreview-seller@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review
@@ -584,39 +641,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 16:55:18 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Logística Multicanal de Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Ahorra un 20 % en las tarifas de Logística Multicanal a partir del 25 de junio</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
  Ya están disponibles dos nuevos programas de descuentos para los vendedores aptos
@@ -630,39 +687,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 16:38:54 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale di Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Tariffe di Gestione multicanale: sconto del 20% dal 25 giugno</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
  Due nuovi programmi di sconto sono ora disponibili per i venditori idonei
@@ -676,39 +733,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 02:40:59 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 05/2026</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -726,39 +783,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 00:17:48 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -788,39 +845,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:43:35 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $143.78 in an attempt to settle your Amazon seller account balance.
@@ -836,39 +893,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 01:13:32 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq5h330940)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -893,39 +950,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 06:55:02 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7kDrHSJf1h)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -945,39 +1002,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 03:26:42 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -993,39 +1050,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 13:57:34 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Iot4D83CtY)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1045,39 +1102,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:36 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1097,39 +1154,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1149,39 +1206,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 14:37:25 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1198,39 +1255,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1250,39 +1307,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:43:44 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1302,39 +1359,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:42:27 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1354,39 +1411,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 14:51:20 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -1402,39 +1459,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 13:35:40 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1451,40 +1508,40 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:31:42 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS -
  APPEAL</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS - APPEAL
@@ -1505,39 +1562,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:48 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1555,39 +1612,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:09:04 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1605,39 +1662,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:43 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1655,39 +1712,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:07:21 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1705,39 +1762,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 06:06:12 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>帮您免费一站式搞定VAT、EPR等合规问题！亚马逊合规服务商城现已正式上线！</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>亚马逊合规服务商城正式上线，一站式帮助卖家高效搞定欧洲站点的VAT、EPR等合规问题。
 			尊敬的 深圳市微海众信科技有限公司,
@@ -1767,39 +1824,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 17:40:38 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1818,40 +1875,40 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 11:02:38 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -1864,39 +1921,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:40 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -1912,39 +1969,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:32 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -1958,40 +2015,40 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:31 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -2007,39 +2064,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:08:15 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -2055,40 +2112,40 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 15:14:09 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2104,39 +2161,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 15:14:03 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -2152,39 +2209,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:04 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -2200,39 +2257,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:01 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -2246,40 +2303,40 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:10:00 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -2295,39 +2352,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 16:07:29 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -2343,39 +2400,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 15:12:02 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -2391,40 +2448,40 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2440,39 +2497,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 23:39:40 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para junio</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para junio
@@ -2501,39 +2558,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 17:10:26 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -2549,40 +2606,40 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 15:13:11 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Tu cuenta cumple ahora nuestros requisitos de registro a efectos
  fiscales en Europa</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -2607,39 +2664,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 15:09:37 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Twoje konto spełnia już europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -2664,39 +2721,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 10:15:12 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -2726,39 +2783,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Tue, 26 May 2026 12:22:30 +0000 (UTC)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>TikTok Shop &lt;tiktokshopseller@shop.tiktok.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>借助这些高潜力商品加速你的业务成长</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  借助这些高潜力商品加速你的业务成长
@@ -2851,39 +2908,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 20:10:01 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
@@ -2899,39 +2956,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 04:57:03 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-11</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2954,39 +3011,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 03:41:21 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -3010,39 +3067,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 03:00:56 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -3065,39 +3122,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 02:44:04 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (y8kVKdPDvp)</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3117,39 +3174,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:33:15 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $105.47 in an attempt to settle your Amazon seller account balance.
@@ -3165,39 +3222,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 02:39:33 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -3223,39 +3280,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3271,39 +3328,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3328,39 +3385,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3380,39 +3437,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3432,39 +3489,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3484,39 +3541,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3537,39 +3594,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3589,39 +3646,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3641,39 +3698,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -3689,39 +3746,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 14:39:47 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3741,39 +3798,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:30:35 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3793,39 +3850,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:29:45 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3842,39 +3899,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:22:00 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3894,39 +3951,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:11 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3946,39 +4003,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:21:19 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -3995,39 +4052,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:07:05 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January-March 2026</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -4044,39 +4101,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 14:48:57 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4096,39 +4153,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:42 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -4152,39 +4209,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:19 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -4208,39 +4265,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 13:46:45 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4260,39 +4317,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:49:45 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4312,39 +4369,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:47:51 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4364,39 +4421,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:36:52 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4416,39 +4473,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:51:22 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -4464,39 +4521,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:50:04 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4513,39 +4570,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:49:55 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4565,39 +4622,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -4614,39 +4671,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4663,39 +4720,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4715,39 +4772,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4767,39 +4824,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4816,39 +4873,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -4863,39 +4920,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -4911,40 +4968,40 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:58:41 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.ca" &lt;cscompliance-docreview-vendor@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC - DOC REVIEW
@@ -4961,40 +5018,40 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:53:39 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -5011,40 +5068,40 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:49:38 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC - DOC REVIEW
@@ -5061,39 +5118,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:02:52 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -5113,40 +5170,40 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:57:24 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -5162,40 +5219,40 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:55:04 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.fr" &lt;cscompliance-docreview-seller@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review
@@ -5211,39 +5268,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:11:27 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -5262,40 +5319,40 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5311,40 +5368,40 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5358,40 +5415,40 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5405,40 +5462,40 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -5451,39 +5508,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -5503,39 +5560,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -5560,39 +5617,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -5617,40 +5674,40 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5665,40 +5722,40 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5712,40 +5769,40 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5759,41 +5816,41 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -5804,39 +5861,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -5855,39 +5912,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -5911,39 +5968,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5961,39 +6018,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6011,39 +6068,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 17:10:44 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6061,39 +6118,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 08:12:17 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Il team di Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Nuova convalida dei numeri di spedizione attiva da oggi</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiorniamo i parametri di convalida dei numeri di spedizione per le spedizioni con corrieri non affiliati, includendo controlli relativi alla lunghezza, al formato previsto del corriere e ai requisiti aggiuntivi relativi ai caratteri. Questo ci permetterà di elaborare il tuo inventario più velocemente.
@@ -6104,39 +6161,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 07:52:06 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Disponible desde hoy la nueva validación del número de seguimiento</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Hemos añadido parámetros de validación del número de seguimiento en los envíos con transportistas no asociados para comprobar la longitud, formato previsto del transportista y requisitos de caracteres adicionales y así procesar tu inventario más rápido.
@@ -6148,39 +6205,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 17:10:56 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6196,39 +6253,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 08:56:06 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>5月27日前入库助力Prime Day成功</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -6258,39 +6315,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:06:09 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6305,39 +6362,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 13:00:10 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Seller News: May 2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6352,39 +6409,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 10:15:46 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -6399,39 +6456,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 15:00:47 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6446,39 +6503,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:37 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6493,39 +6550,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:10:53 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -6543,39 +6600,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:55:42 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Ship Smarter: Get 3 FREE Brokerage Fees: Limited Time C2S2 Offer 🚀</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z3hy11/6664114770/h/cIM7P1R6ABFsNRmzeIU2ASpTCxzOevVrUjDi2lts12A)
 Ship Cross-Border &amp; Save Big. Get Started with C2S2 Today.
@@ -6592,39 +6649,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 06:33:16 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6643,39 +6700,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:48:46 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6690,40 +6747,40 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 05:21:00 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -6739,39 +6796,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 17:10:29 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6787,39 +6844,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:52:25 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;store-news@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>EchoPlan Magnetic Blocks is still in your cart</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Still thinking about it? https://www.amazon.com/gp/cart/view.html?ref_=cor
 EchoPlan 200PCS Magnetic Blocks, Magnetic Building Blocks, Magnet Blocks Cubes, STEM Educational Stacking Magnet Toy for Kids Ages 3 4 5 6 7 8 9 10 11, Birthday Gifts for Boys and Girls, 1&amp;quot; Large Size
@@ -6840,39 +6897,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:07:42 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6887,39 +6944,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 03:00:00 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -6949,39 +7006,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 16:40:18 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -7009,39 +7066,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:51:48 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
@@ -7057,39 +7114,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 10:10:51 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>EPR Pay on Behalf charges for 2024 Amazon.co.uk sales</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7108,39 +7165,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 12:21:34 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7162,39 +7219,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:22:50 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -7216,39 +7273,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 16:23:48 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -7267,39 +7324,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 08:34:05 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7311,39 +7368,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:22:14 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7355,39 +7412,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:02:56 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
@@ -7399,39 +7456,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:29:17 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7443,39 +7500,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:25:39 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -7487,39 +7544,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:10:57 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7531,39 +7588,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:09:44 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -7582,39 +7639,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:01:18 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -7633,39 +7690,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:25:07 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 4 2026</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 4 i rok 2026.
@@ -7677,39 +7734,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:24:35 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -7721,39 +7778,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:03:04 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -7765,39 +7822,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 20:51:50 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -7809,39 +7866,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:44:14 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 4 2026</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 4 i rok 2026.
@@ -7853,39 +7910,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:35:59 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -7897,39 +7954,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:24:07 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7941,39 +7998,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:18:06 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -7985,39 +8042,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:33:15 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -8029,39 +8086,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:20:52 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -8073,39 +8130,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:43:38 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -8117,39 +8174,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:17:48 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -8161,39 +8218,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:52:53 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -8205,40 +8262,40 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:40:42 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -8257,39 +8314,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:57:28 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -8301,39 +8358,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:43:13 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -8345,39 +8402,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:40:52 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -8389,39 +8446,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:55:06 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -8433,39 +8490,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:49:29 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -8477,39 +8534,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:20:15 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -8530,39 +8587,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8577,39 +8634,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 14:24:59 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -8628,39 +8685,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 05:32:15 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -8682,39 +8739,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 04:06:08 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-04</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8737,39 +8794,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 03:17:21 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8793,39 +8850,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 04:51:55 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8849,39 +8906,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:58:34 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -8902,39 +8959,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:50:26 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8957,39 +9014,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9013,39 +9070,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9068,40 +9125,40 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 07:25:40 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Update VAT registration information to reinstate Inventory and FBA
  functionality of your Amazon.it store</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -9117,39 +9174,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
